--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -50,7 +50,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -91,7 +91,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -398,7 +398,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>2412</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.35">
@@ -414,7 +414,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="1">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.35">

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -414,7 +414,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.35">

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>TARGET RSE</t>
   </si>
@@ -42,6 +42,12 @@
   </si>
   <si>
     <t>DSE PRODUCTIVTY</t>
+  </si>
+  <si>
+    <t>LAST UPDATE</t>
+  </si>
+  <si>
+    <t>18 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>
@@ -89,9 +95,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -373,19 +380,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:C7"/>
+  <dimension ref="B2:F7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -393,7 +408,7 @@
         <v>1616250360</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>2</v>
       </c>
@@ -401,7 +416,7 @@
         <v>2420</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -409,7 +424,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -417,7 +432,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>5</v>
       </c>

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -47,7 +47,7 @@
     <t>LAST UPDATE</t>
   </si>
   <si>
-    <t>18 SEPTEMBER 2026</t>
+    <t>19 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -47,7 +47,7 @@
     <t>LAST UPDATE</t>
   </si>
   <si>
-    <t>19 SEPTEMBER 2026</t>
+    <t>20 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -47,7 +47,7 @@
     <t>LAST UPDATE</t>
   </si>
   <si>
-    <t>20 SEPTEMBER 2026</t>
+    <t>21 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -47,7 +47,7 @@
     <t>LAST UPDATE</t>
   </si>
   <si>
-    <t>21 SEPTEMBER 2026</t>
+    <t>22 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -47,7 +47,7 @@
     <t>LAST UPDATE</t>
   </si>
   <si>
-    <t>22 SEPTEMBER 2026</t>
+    <t>23 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -47,7 +47,7 @@
     <t>LAST UPDATE</t>
   </si>
   <si>
-    <t>23 SEPTEMBER 2026</t>
+    <t>25 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -47,7 +47,7 @@
     <t>LAST UPDATE</t>
   </si>
   <si>
-    <t>25 SEPTEMBER 2026</t>
+    <t>26 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -47,7 +47,7 @@
     <t>LAST UPDATE</t>
   </si>
   <si>
-    <t>26 SEPTEMBER 2026</t>
+    <t>27 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -47,7 +47,7 @@
     <t>LAST UPDATE</t>
   </si>
   <si>
-    <t>27 SEPTEMBER 2026</t>
+    <t>28 SEPTEMBER 2026</t>
   </si>
 </sst>
 </file>

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -47,7 +47,7 @@
     <t>LAST UPDATE</t>
   </si>
   <si>
-    <t>28 SEPTEMBER 2026</t>
+    <t>18 OKTOBER 2026</t>
   </si>
 </sst>
 </file>
@@ -405,7 +405,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>1616250360</v>
+        <v>1292230507</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.35">
@@ -413,7 +413,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>2420</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.35">
@@ -421,7 +421,8 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>155</v>
+        <f>233*80%</f>
+        <v>186.4</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.35">
@@ -429,7 +430,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.35">
@@ -437,7 +438,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>TARGET RSE</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>LAST UPDATE</t>
-  </si>
-  <si>
-    <t>18 OKTOBER 2026</t>
   </si>
 </sst>
 </file>
@@ -98,7 +95,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -396,8 +393,8 @@
       <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>7</v>
+      <c r="F2" s="2">
+        <v>46316</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -394,7 +394,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -394,7 +394,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>46317</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -394,7 +394,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>46319</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -394,7 +394,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>46320</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">

--- a/TARGET RSE.xlsx
+++ b/TARGET RSE.xlsx
@@ -394,7 +394,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>46323</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">
